--- a/artfynd/A 14463-2026 artfynd.xlsx
+++ b/artfynd/A 14463-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>133178441</v>
       </c>
       <c r="B2" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -785,11 +785,11 @@
         <v>133178552</v>
       </c>
       <c r="B3" t="n">
-        <v>79348</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133178553</v>
+        <v>133178440</v>
       </c>
       <c r="B4" t="n">
-        <v>79372</v>
+        <v>79397</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730802</v>
+        <v>730850</v>
       </c>
       <c r="R4" t="n">
-        <v>7124515</v>
+        <v>7124556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133178440</v>
+        <v>133178553</v>
       </c>
       <c r="B5" t="n">
-        <v>79372</v>
+        <v>79397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730850</v>
+        <v>730802</v>
       </c>
       <c r="R5" t="n">
-        <v>7124556</v>
+        <v>7124515</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,6 +1100,225 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133178554</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79397</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Degerforsheden, Rosinedal, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>730813</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7124583</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133178551</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Degerforsheden, Rosinedal, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>730790</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7124483</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14463-2026 artfynd.xlsx
+++ b/artfynd/A 14463-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133178441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133178552</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133178440</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133178553</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133178554</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,8 +1349,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133178551</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>